--- a/raw_data_template.xlsx
+++ b/raw_data_template.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,8 @@
     <col width="26" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
     <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -619,6 +621,16 @@
       <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Zalora Images</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
         </is>
       </c>
     </row>
@@ -731,6 +743,16 @@
           <t>Zalora's own image set, separated by ' ; '. Zalora requires different image dimensions/crops than the other 3 marketplaces, so give it its own set here rather than reusing Parent/Variant Images.</t>
         </is>
       </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>For Zalora's Season column.</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>For Zalora's Year column.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -849,6 +871,14 @@
         <is>
           <t>https://example.com/zalora1.jpg ; https://example.com/zalora2.jpg</t>
         </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
